--- a/artfynd/A 65201-2023 artfynd.xlsx
+++ b/artfynd/A 65201-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65201-2023 artfynd.xlsx
+++ b/artfynd/A 65201-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117884043</v>
+        <v>117884016</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
+        <v>74584</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,35 +799,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456422</v>
+        <v>456368</v>
       </c>
       <c r="R3" t="n">
-        <v>6620612</v>
+        <v>6620473</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,6 +886,26 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre granskog med hög luftfuktiget</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>På murken björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Betula # På murken björkhögstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1029,7 +1044,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117884056</v>
+        <v>117884043</v>
       </c>
       <c r="B5" t="n">
         <v>97836</v>
@@ -1073,14 +1088,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>N Lostjärn, Vrm</t>
+          <t>N Lostjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456402</v>
+        <v>456422</v>
       </c>
       <c r="R5" t="n">
-        <v>6620629</v>
+        <v>6620612</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,6 +1139,16 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre granskog med hög luftfuktiget</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1140,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117884016</v>
+        <v>117884030</v>
       </c>
       <c r="B6" t="n">
-        <v>74584</v>
+        <v>95384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,26 +1181,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1183,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456368</v>
+        <v>456422</v>
       </c>
       <c r="R6" t="n">
-        <v>6620473</v>
+        <v>6620558</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,22 +1269,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>På murken björkhögstubbe</t>
+          <t>På barklös, klen tallåga</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Betula # På murken björkhögstubbe</t>
+          <t>Pinus sylvestris # På barklös, klen tallåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1276,10 +1302,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117884030</v>
+        <v>117884056</v>
       </c>
       <c r="B7" t="n">
-        <v>95384</v>
+        <v>97836</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,42 +1314,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N Lostjärnen, Vrm</t>
+          <t>N Lostjärn, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456422</v>
+        <v>456402</v>
       </c>
       <c r="R7" t="n">
-        <v>6620558</v>
+        <v>6620629</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,36 +1397,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre granskog med hög luftfuktiget</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>På barklös, klen tallåga</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På barklös, klen tallåga</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 65201-2023 artfynd.xlsx
+++ b/artfynd/A 65201-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117884016</v>
+        <v>117884030</v>
       </c>
       <c r="B3" t="n">
-        <v>74584</v>
+        <v>95386</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,26 +803,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456368</v>
+        <v>456422</v>
       </c>
       <c r="R3" t="n">
-        <v>6620473</v>
+        <v>6620558</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,22 +891,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>På murken björkhögstubbe</t>
+          <t>På barklös, klen tallåga</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Betula # På murken björkhögstubbe</t>
+          <t>Pinus sylvestris # På barklös, klen tallåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -923,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117884071</v>
+        <v>117884016</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>74586</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,35 +936,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -971,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456389</v>
+        <v>456368</v>
       </c>
       <c r="R4" t="n">
-        <v>6620677</v>
+        <v>6620473</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1027,6 +1023,26 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Äldre granskog med hög luftfuktiget</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>På murken björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Betula # På murken björkhögstubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1047,7 +1063,7 @@
         <v>117884043</v>
       </c>
       <c r="B5" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1165,10 +1181,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117884030</v>
+        <v>117884071</v>
       </c>
       <c r="B6" t="n">
-        <v>95384</v>
+        <v>97838</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,30 +1193,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1209,10 +1229,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456422</v>
+        <v>456389</v>
       </c>
       <c r="R6" t="n">
-        <v>6620558</v>
+        <v>6620677</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1265,26 +1285,6 @@
       <c r="AI6" t="inlineStr">
         <is>
           <t>Äldre granskog med hög luftfuktiget</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>På barklös, klen tallåga</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På barklös, klen tallåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1305,7 +1305,7 @@
         <v>117884056</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 65201-2023 artfynd.xlsx
+++ b/artfynd/A 65201-2023 artfynd.xlsx
@@ -1416,7 +1416,7 @@
         <v>121344569</v>
       </c>
       <c r="B8" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 65201-2023 artfynd.xlsx
+++ b/artfynd/A 65201-2023 artfynd.xlsx
@@ -1416,7 +1416,7 @@
         <v>121344569</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 65201-2023 artfynd.xlsx
+++ b/artfynd/A 65201-2023 artfynd.xlsx
@@ -1416,7 +1416,7 @@
         <v>121344569</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 65201-2023 artfynd.xlsx
+++ b/artfynd/A 65201-2023 artfynd.xlsx
@@ -1416,7 +1416,7 @@
         <v>121344569</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 65201-2023 artfynd.xlsx
+++ b/artfynd/A 65201-2023 artfynd.xlsx
@@ -1416,7 +1416,7 @@
         <v>121344569</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 65201-2023 artfynd.xlsx
+++ b/artfynd/A 65201-2023 artfynd.xlsx
@@ -1416,7 +1416,7 @@
         <v>121344569</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 65201-2023 artfynd.xlsx
+++ b/artfynd/A 65201-2023 artfynd.xlsx
@@ -1416,7 +1416,7 @@
         <v>121344569</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 65201-2023 artfynd.xlsx
+++ b/artfynd/A 65201-2023 artfynd.xlsx
@@ -675,50 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5008870</v>
+        <v>117884030</v>
       </c>
       <c r="B2" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>, Vrm</t>
+          <t>N Lostjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456321.9657552714</v>
+        <v>456422</v>
       </c>
       <c r="R2" t="n">
-        <v>6620229.702414036</v>
+        <v>6620558</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,18 +758,49 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre granskog med hög luftfuktiget</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>På barklös, klen tallåga</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På barklös, klen tallåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Flora Värmland</t>
+          <t>Emma Enfjäll</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Flora Värmland</t>
+          <t>Emma Enfjäll</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,12 +810,7 @@
         <v>117884016</v>
       </c>
       <c r="B3" t="n">
-        <v>74588</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,15 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117884056</v>
+        <v>117884043</v>
       </c>
       <c r="B4" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,14 +977,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N Lostjärn, Vrm</t>
+          <t>N Lostjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456402</v>
+        <v>456422</v>
       </c>
       <c r="R4" t="n">
-        <v>6620629</v>
+        <v>6620612</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,6 +1028,16 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre granskog med hög luftfuktiget</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1034,54 +1054,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117884030</v>
+        <v>117884056</v>
       </c>
       <c r="B5" t="n">
-        <v>95606</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>N Lostjärnen, Vrm</t>
+          <t>N Lostjärn, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456422</v>
+        <v>456402</v>
       </c>
       <c r="R5" t="n">
-        <v>6620558</v>
+        <v>6620629</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,36 +1144,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre granskog med hög luftfuktiget</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>På barklös, klen tallåga</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På barklös, klen tallåga</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1171,15 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117884043</v>
+        <v>117884071</v>
       </c>
       <c r="B6" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456422</v>
+        <v>456389</v>
       </c>
       <c r="R6" t="n">
-        <v>6620612</v>
+        <v>6620677</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1292,15 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117884071</v>
+        <v>121344569</v>
       </c>
       <c r="B7" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,24 +1305,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>knoppbristning</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N Lostjärnen, Vrm</t>
+          <t>Liselund, SV om, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456389</v>
+        <v>456402</v>
       </c>
       <c r="R7" t="n">
-        <v>6620677</v>
+        <v>6620628</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,6 +1344,11 @@
           <t>Färnebo</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>S-Fil-0217</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
           <t>2024-06-19</t>
@@ -1378,20 +1359,19 @@
           <t>2024-06-19</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3 dellokaler rapporterade. RT90: 6623453-1411085; 6623502-1411072 samt 6623436-1411104. Samtliga 10 m noggrannhet. Ingen mängduppgift.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
@@ -1401,67 +1381,61 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>Emma Enfjäll</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Emma Enfjäll</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121344569</v>
+        <v>5008870</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Liselund, SV om, Vrm</t>
+          <t>Lostjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456402</v>
+        <v>456322</v>
       </c>
       <c r="R8" t="n">
-        <v>6620628</v>
+        <v>6620230</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1486,24 +1460,14 @@
           <t>Färnebo</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>S-Fil-0217</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>3 dellokaler rapporterade. RT90: 6623453-1411085; 6623502-1411072 samt 6623436-1411104. Samtliga 10 m noggrannhet. Ingen mängduppgift.</t>
+          <t>2000-12-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,28 +1478,19 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre granskog med hög luftfuktiget</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Flora Värmland</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Enfjäll</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Flora Värmland</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65201-2023 artfynd.xlsx
+++ b/artfynd/A 65201-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -804,6 +809,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117884030</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -935,6 +945,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117884016</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1051,6 +1066,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117884043</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1157,6 +1177,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117884056</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1273,6 +1298,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117884071</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1394,6 +1424,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121344569</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1491,8 +1526,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5008870</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>